--- a/stories/arbres/TREE-REL-009.xlsx
+++ b/stories/arbres/TREE-REL-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|À la ferme, Sara a entendu un rire pas gentil, près des poules. Sara a même souri un peu, par surprise. Maman est près du portail. Papa parle au fermier. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Près d'une pomme, Sara a entendu le rire. C'est une pomme. Le sable est un peu frais. Sara s'approche, sans courir. Papa n'est pas loin. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Il s'est passé un rire pas gentil. Que fait-on ? Avec une pomme.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2250,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi la cuisine, après une pomme. Un oiseau siffle tout près. Sara touche la cuisine tout doucement. Maman dit : je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+          <t>Sara a choisi la cuisine, après une pomme. Un oiseau siffle tout près. Sara touche la cuisine tout doucement. Je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2388,13 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la cuisine, après une pomme. Un oiseau siffle tout près. Sara touche la cuisine tout doucement.
+maman|Je suis là.
+narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après une pomme et la cuisine. La tasse est encore tiède. On dit merci. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On laisse les cubes à sa place. Sara est près de maman. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après une pomme et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3199,7 +3278,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Maman dit : je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
+          <t>Sara rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3337,6 +3416,12 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.
+maman|Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3584,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3751,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le jardin, après une pomme. Un crayon sent le bois. On parle du jardin. Sara écoute jusqu'au bout. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3942,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4109,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après une pomme et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On laisse les cubes à sa place. Sara est près de maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4276,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4443,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après une pomme et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4610,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4519,7 +4639,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Maman dit : je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
+          <t>Sara rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4657,6 +4777,13 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la chambre, après une pomme. Un gravier roule sous une semelle. Sara range un peu autour de la chambre. Elle respire. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après une pomme et la chambre. Un pigeon roucoule. On essuie une miette. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après une pomme et la chambre. La cuillère tinte. On referme un livre. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après une pomme et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose la dînette et va vers maman. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6473,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Près d'un yaourt, Sara a entendu le rire. Sara s'occupe de un yaourt. Le soleil chauffe un peu le nez. Maman sourit. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6654,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Il s'est passé un rire pas gentil. Que fait-on ? Avec un yaourt.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6827,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7018,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7185,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la cuisine, après un yaourt. Une vache meugle, loin. Sara range un peu autour de la cuisine. Elle respire. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7376,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7543,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après un yaourt et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7710,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7527,7 +7739,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Maman dit : je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
+          <t>Sara rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7665,6 +7877,13 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8046,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8213,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après un yaourt et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On laisse la dînette à sa place. Sara est près de maman. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8380,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8175,7 +8409,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le jardin, après un yaourt. La laine du doudou est douce. Sara touche le jardin tout doucement. Maman dit : je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+          <t>Sara a choisi le jardin, après un yaourt. La laine du doudou est douce. Sara touche le jardin tout doucement. Je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8313,6 +8547,13 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le jardin, après un yaourt. La laine du doudou est douce. Sara touche le jardin tout doucement.
+maman|Je suis là.
+narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8740,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8907,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après un yaourt et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9074,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9241,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après un yaourt et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose le livre et va vers maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9408,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9575,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après un yaourt et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9742,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9495,7 +9771,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi la chambre, après un yaourt. Le savon sent la fleur. Sara touche la chambre tout doucement. Maman dit : je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+          <t>Sara a choisi la chambre, après un yaourt. Le savon sent la fleur. Sara touche la chambre tout doucement. Je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9633,6 +9909,13 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la chambre, après un yaourt. Le savon sent la fleur. Sara touche la chambre tout doucement.
+maman|Je suis là.
+narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10102,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10269,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après un yaourt et la chambre. Une plume vole. On range les chaussures. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10436,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10603,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après un yaourt et la chambre. Le pain croustille. On met le doudou près de soi. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose le livre et va vers maman. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10770,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10937,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après un yaourt et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11104,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11271,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Près d'un morceau de pain, Sara a entendu le rire. Voilà un morceau de pain. Un coq chante une fois. Sara pose les pieds par terre, près de maman. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11452,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Il s'est passé un rire pas gentil. Que fait-on ? Avec un morceau de pain.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11625,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11816,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11507,7 +11845,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi la cuisine, après un morceau de pain. Le parquet craque un tout petit peu. Sara touche la cuisine tout doucement. Maman dit : je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+          <t>Sara a choisi la cuisine, après un morceau de pain. Le parquet craque un tout petit peu. Sara touche la cuisine tout doucement. Je suis là. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11645,6 +11983,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la cuisine, après un morceau de pain. Le parquet craque un tout petit peu. Sara touche la cuisine tout doucement.
+maman|Je suis là.
+narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12176,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12343,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après un morceau de pain et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12510,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12677,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après un morceau de pain et la cuisine. Le train souffle au loin. On pose le sac. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12844,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13011,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après un morceau de pain et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara range la dînette un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13178,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13345,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le jardin, après un morceau de pain. Le savon sent la fleur. Sara s'installe avec le jardin. Maman reste à portée de voix. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13536,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13175,7 +13565,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Maman dit : je t'ai entendu. Papa aussi. On gardu geste.</t>
+          <t>Sara rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Je t'ai entendu. Papa aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13313,6 +13703,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.
+maman|Je t'ai entendu. Papa aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13871,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14038,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après un morceau de pain et le jardin. Le bois de la table est lisse. On attend la réponse. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14205,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14372,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après un morceau de pain et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14539,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14706,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la chambre, après un morceau de pain. Un oiseau siffle tout près. Sara range un peu autour de la chambre. Elle respire. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14897,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15064,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint les cubes, après un morceau de pain et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15231,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15398,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le livre, après un morceau de pain et la chambre. La clochette de la porte tinte. On dit stop, tout clair. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15565,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15732,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint la dînette, après un morceau de pain et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15899,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15939,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-009.xlsx
+++ b/stories/arbres/TREE-REL-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|À la ferme, Sara a entendu un rire pas gentil, près des poules. Sara a même souri un peu, par surprise. Maman est près du portail. Papa parle au fermier. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Près d'une pomme, Sara a entendu le rire. C'est une pomme. Le sable est un peu frais. Sara s'approche, sans courir. Papa n'est pas loin. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Il s'est passé un rire pas gentil. Que fait-on ? Avec une pomme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
 narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2766,7 @@
           <t>narrateur|Sara rejoint les cubes, après une pomme et la cuisine. La tasse est encore tiède. On dit merci. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On laisse les cubes à sa place. Sara est près de maman. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3102,7 @@
           <t>narrateur|Sara rejoint le livre, après une pomme et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3422,6 +3439,7 @@
 maman|Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3589,6 +3607,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3756,6 +3775,7 @@
           <t>narrateur|Sara a choisi le jardin, après une pomme. Un crayon sent le bois. On parle du jardin. Sara écoute jusqu'au bout. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3947,6 +3967,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4114,6 +4135,7 @@
           <t>narrateur|Sara rejoint les cubes, après une pomme et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On laisse les cubes à sa place. Sara est près de maman. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4281,6 +4303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4448,6 +4471,7 @@
           <t>narrateur|Sara rejoint le livre, après une pomme et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4615,6 +4639,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Sara a choisi la chambre, après une pomme. Un gravier roule sous une semelle. Sara range un peu autour de la chambre. Elle respire. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Sara rejoint les cubes, après une pomme et la chambre. Un pigeon roucoule. On essuie une miette. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Sara rejoint le livre, après une pomme et la chambre. La cuillère tinte. On referme un livre. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Sara rejoint la dînette, après une pomme et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose la dînette et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6478,6 +6513,7 @@
           <t>narrateur|Près d'un yaourt, Sara a entendu le rire. Sara s'occupe de un yaourt. Le soleil chauffe un peu le nez. Maman sourit. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6661,6 +6697,7 @@
           <t>narrateur|Il s'est passé un rire pas gentil. Que fait-on ? Avec un yaourt.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6832,6 +6869,7 @@
           <t>narrateur|Oui. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7023,6 +7061,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7190,6 +7229,7 @@
           <t>narrateur|Sara a choisi la cuisine, après un yaourt. Une vache meugle, loin. Sara range un peu autour de la cuisine. Elle respire. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7381,6 +7421,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7548,6 +7589,7 @@
           <t>narrateur|Sara rejoint les cubes, après un yaourt et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7715,6 +7757,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7884,6 +7927,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8051,6 +8095,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8218,6 +8263,7 @@
           <t>narrateur|Sara rejoint la dînette, après un yaourt et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On laisse la dînette à sa place. Sara est près de maman. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8385,6 +8431,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8554,6 +8601,7 @@
 narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8745,6 +8793,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8912,6 +8961,7 @@
           <t>narrateur|Sara rejoint les cubes, après un yaourt et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9079,6 +9129,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9246,6 +9297,7 @@
           <t>narrateur|Sara rejoint le livre, après un yaourt et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose le livre et va vers maman. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9413,6 +9465,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9580,6 +9633,7 @@
           <t>narrateur|Sara rejoint la dînette, après un yaourt et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9747,6 +9801,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9916,6 +9971,7 @@
 narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10107,6 +10163,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10274,6 +10331,7 @@
           <t>narrateur|Sara rejoint les cubes, après un yaourt et la chambre. Une plume vole. On range les chaussures. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10441,6 +10499,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10608,6 +10667,7 @@
           <t>narrateur|Sara rejoint le livre, après un yaourt et la chambre. Le pain croustille. On met le doudou près de soi. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose le livre et va vers maman. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10775,6 +10835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10942,6 +11003,7 @@
           <t>narrateur|Sara rejoint la dînette, après un yaourt et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11109,6 +11171,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
           <t>narrateur|Près d'un morceau de pain, Sara a entendu le rire. Voilà un morceau de pain. Un coq chante une fois. Sara pose les pieds par terre, près de maman. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11459,6 +11523,7 @@
           <t>narrateur|Il s'est passé un rire pas gentil. Que fait-on ? Avec un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11630,6 +11695,7 @@
           <t>narrateur|Oui. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11821,6 +11887,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11990,6 +12057,7 @@
 narrateur|Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12181,6 +12249,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12348,6 +12417,7 @@
           <t>narrateur|Sara rejoint les cubes, après un morceau de pain et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12515,6 +12585,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12682,6 +12753,7 @@
           <t>narrateur|Sara rejoint le livre, après un morceau de pain et la cuisine. Le train souffle au loin. On pose le sac. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12849,6 +12921,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13016,6 +13089,7 @@
           <t>narrateur|Sara rejoint la dînette, après un morceau de pain et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara range la dînette un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13183,6 +13257,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13350,6 +13425,7 @@
           <t>narrateur|Sara a choisi le jardin, après un morceau de pain. Le savon sent la fleur. Sara s'installe avec le jardin. Maman reste à portée de voix. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13541,6 +13617,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13709,6 +13786,7 @@
 maman|Je t'ai entendu. Papa aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13876,6 +13954,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14043,6 +14122,7 @@
           <t>narrateur|Sara rejoint le livre, après un morceau de pain et le jardin. Le bois de la table est lisse. On attend la réponse. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14210,6 +14290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14377,6 +14458,7 @@
           <t>narrateur|Sara rejoint la dînette, après un morceau de pain et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara serre la main de maman, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14544,6 +14626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14711,6 +14794,7 @@
           <t>narrateur|Sara a choisi la chambre, après un morceau de pain. Un oiseau siffle tout près. Sara range un peu autour de la chambre. Elle respire. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14902,6 +14986,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15069,6 +15154,7 @@
           <t>narrateur|Sara rejoint les cubes, après un morceau de pain et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15236,6 +15322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15403,6 +15490,7 @@
           <t>narrateur|Sara rejoint le livre, après un morceau de pain et la chambre. La clochette de la porte tinte. On dit stop, tout clair. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. Sara boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15570,6 +15658,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15737,6 +15826,7 @@
           <t>narrateur|Sara rejoint la dînette, après un morceau de pain et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. Sara raconte à papa ou maman. Même si on a ri, on raconte. Maman écoute. Papa peut écouter aussi. On écoute le silence une seconde. Sara est assise. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15904,6 +15994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15922,7 +16013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15946,6 +16037,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15960,7 +16065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16147,6 +16252,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
